--- a/Aniversarios.xlsx
+++ b/Aniversarios.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielnatacardoso/Library/CloudStorage/Dropbox/Potenza - Operacional/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielnatacardoso/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDAA419-E14E-E544-BB03-F001B20706C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655EF1BB-B676-0342-88DD-3FFF74134C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16680" xr2:uid="{F74D5877-3B65-4C77-869E-BA5EDDF9A148}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="48">
   <si>
     <t>Gabriel Flores</t>
   </si>
@@ -125,15 +125,9 @@
     <t>Douglas</t>
   </si>
   <si>
-    <t>Bravia Consulting</t>
-  </si>
-  <si>
     <t>Sandrini</t>
   </si>
   <si>
-    <t>Bravia &amp; Co</t>
-  </si>
-  <si>
     <t>Augusto</t>
   </si>
   <si>
@@ -170,13 +164,25 @@
     <t>Tipo</t>
   </si>
   <si>
-    <t>Potenza, Baron, Liven, ABC, Bravia Consulting, Costa Brava, Candeias</t>
-  </si>
-  <si>
     <t>rafael.rucinski@potenza-investimentos.com</t>
   </si>
   <si>
     <t>Baron, Liven</t>
+  </si>
+  <si>
+    <t>Potenza, Baron, Liven, ABC, Bravia Consulting, Costa Brava, Candeias, Navepark, Bravia &amp; Co</t>
+  </si>
+  <si>
+    <t>Potenza, Costa Brava</t>
+  </si>
+  <si>
+    <t>Bravia &amp; Co, Bravia Consulting, Candeias</t>
+  </si>
+  <si>
+    <t>Bravia Consulting, Bravia &amp; Co, Candeias</t>
+  </si>
+  <si>
+    <t>danielnata14@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -662,19 +668,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F1" s="4"/>
     </row>
@@ -692,7 +698,7 @@
         <v>46025</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -710,7 +716,7 @@
         <v>45322</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F3" s="4"/>
     </row>
@@ -728,7 +734,7 @@
         <v>46054</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F4" s="4"/>
     </row>
@@ -746,7 +752,7 @@
         <v>45325</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -764,7 +770,7 @@
         <v>45337</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F6" s="4"/>
     </row>
@@ -782,7 +788,7 @@
         <v>45350</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -800,13 +806,13 @@
         <v>45386</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
@@ -818,7 +824,7 @@
         <v>36265</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -836,7 +842,7 @@
         <v>33343</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -848,31 +854,31 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1">
         <v>36633</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D12" s="1">
         <v>46142</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F12" s="4"/>
     </row>
@@ -890,7 +896,7 @@
         <v>45422</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F13" s="4"/>
     </row>
@@ -908,7 +914,7 @@
         <v>45432</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F14" s="4"/>
     </row>
@@ -926,7 +932,7 @@
         <v>45461</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F15" s="4"/>
     </row>
@@ -937,14 +943,14 @@
       <c r="B16" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>28</v>
+      <c r="C16" t="s">
+        <v>46</v>
       </c>
       <c r="D16" s="10">
         <v>46212</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -962,7 +968,7 @@
         <v>45497</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -980,7 +986,7 @@
         <v>45499</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F18" s="4"/>
     </row>
@@ -998,13 +1004,13 @@
         <v>46248</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
@@ -1016,7 +1022,7 @@
         <v>36037</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F20" s="4"/>
     </row>
@@ -1028,31 +1034,31 @@
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D21" s="1">
         <v>45559</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D22" s="1">
         <v>46326</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F22" s="4"/>
     </row>
@@ -1070,13 +1076,13 @@
         <v>45597</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
         <v>2</v>
@@ -1088,25 +1094,25 @@
         <v>46342</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D25" s="10">
         <v>29178</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F25" s="4"/>
     </row>
@@ -1124,7 +1130,7 @@
         <v>45617</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F26" s="4"/>
     </row>
@@ -1142,13 +1148,13 @@
         <v>45618</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
@@ -1160,7 +1166,7 @@
         <v>45632</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F28" s="4"/>
     </row>
